--- a/Assets/StreamingAssets/id注解.xlsx
+++ b/Assets/StreamingAssets/id注解.xlsx
@@ -1,20 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18468" windowHeight="10007"/>
+    <workbookView windowWidth="16650" windowHeight="11655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="17">
   <si>
     <t>id</t>
   </si>
@@ -59,12 +72,18 @@
   </si>
   <si>
     <t>亮度墙</t>
+  </si>
+  <si>
+    <t>Key（钥匙）</t>
+  </si>
+  <si>
+    <t>MagicDoor（魔法门）</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -80,34 +99,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -121,14 +112,6 @@
       <color rgb="FF800080"/>
       <name val="等线"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -173,6 +156,21 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="等线"/>
       <charset val="0"/>
@@ -218,7 +216,28 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -233,49 +252,133 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -287,121 +390,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -424,21 +443,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -471,6 +475,21 @@
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -529,148 +548,148 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -684,52 +703,52 @@
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
-    <cellStyle name="输入" xfId="3" builtinId="20"/>
-    <cellStyle name="货币" xfId="4" builtinId="4"/>
-    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
-    <cellStyle name="差" xfId="7" builtinId="27"/>
-    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
-    <cellStyle name="超链接" xfId="10" builtinId="8"/>
-    <cellStyle name="百分比" xfId="11" builtinId="5"/>
-    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
-    <cellStyle name="注释" xfId="13" builtinId="10"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
     <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
-    <cellStyle name="标题" xfId="17" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
-    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="计算" xfId="25" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
-    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
-    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
-    <cellStyle name="汇总" xfId="30" builtinId="25"/>
-    <cellStyle name="好" xfId="31" builtinId="26"/>
-    <cellStyle name="适中" xfId="32" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
-    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
-    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
-    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
-    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
@@ -1001,15 +1020,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C29"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="18.6296296296296" style="1" customWidth="1"/>
+    <col min="2" max="2" width="26.375" style="1" customWidth="1"/>
     <col min="3" max="3" width="10.25" style="1" customWidth="1"/>
     <col min="4" max="4" width="18.75" style="1" customWidth="1"/>
     <col min="5" max="5" width="20.75" style="1" customWidth="1"/>
-    <col min="6" max="6" width="20.8796296296296" style="1" customWidth="1"/>
-    <col min="7" max="7" width="20.6296296296296" style="1" customWidth="1"/>
+    <col min="6" max="6" width="20.8833333333333" style="1" customWidth="1"/>
+    <col min="7" max="7" width="20.6333333333333" style="1" customWidth="1"/>
     <col min="8" max="8" width="20" style="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
@@ -1224,6 +1243,9 @@
         <f t="shared" si="1"/>
         <v>10015</v>
       </c>
+      <c r="B17" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="C17" s="1">
         <f t="shared" si="0"/>
         <v>20015</v>
@@ -1233,6 +1255,9 @@
       <c r="A18" s="1">
         <f t="shared" si="1"/>
         <v>10016</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="C18" s="1">
         <f t="shared" si="0"/>

--- a/Assets/StreamingAssets/id注解.xlsx
+++ b/Assets/StreamingAssets/id注解.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="18">
   <si>
     <t>id</t>
   </si>
@@ -78,6 +78,9 @@
   </si>
   <si>
     <t>MagicDoor（魔法门）</t>
+  </si>
+  <si>
+    <t>气泡</t>
   </si>
 </sst>
 </file>
@@ -1269,6 +1272,9 @@
         <f t="shared" si="1"/>
         <v>10017</v>
       </c>
+      <c r="B19" s="1" t="s">
+        <v>17</v>
+      </c>
       <c r="C19" s="1">
         <f t="shared" si="0"/>
         <v>20017</v>

--- a/Assets/StreamingAssets/id注解.xlsx
+++ b/Assets/StreamingAssets/id注解.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="16650" windowHeight="11655"/>
+    <workbookView windowWidth="19755" windowHeight="11655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="20">
   <si>
     <t>id</t>
   </si>
@@ -81,6 +81,12 @@
   </si>
   <si>
     <t>气泡</t>
+  </si>
+  <si>
+    <t>箱子</t>
+  </si>
+  <si>
+    <t>相机组触发器</t>
   </si>
 </sst>
 </file>
@@ -1285,6 +1291,9 @@
         <f t="shared" si="1"/>
         <v>10018</v>
       </c>
+      <c r="B20" s="1" t="s">
+        <v>18</v>
+      </c>
       <c r="C20" s="1">
         <f t="shared" si="0"/>
         <v>20018</v>
@@ -1294,6 +1303,9 @@
       <c r="A21" s="1">
         <f t="shared" si="1"/>
         <v>10019</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="C21" s="1">
         <f t="shared" si="0"/>

--- a/Assets/StreamingAssets/id注解.xlsx
+++ b/Assets/StreamingAssets/id注解.xlsx
@@ -1,33 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19755" windowHeight="11655"/>
+    <workbookView windowWidth="18468" windowHeight="10007"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="21">
   <si>
     <t>id</t>
   </si>
@@ -87,12 +74,15 @@
   </si>
   <si>
     <t>相机组触发器</t>
+  </si>
+  <si>
+    <t>测试用boss</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -108,6 +98,34 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -121,6 +139,14 @@
       <color rgb="FF800080"/>
       <name val="等线"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -165,14 +191,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF3F3F3F"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -180,7 +199,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFA7D00"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -188,6 +207,13 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="等线"/>
       <charset val="0"/>
@@ -196,21 +222,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
       <charset val="0"/>
@@ -225,28 +236,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -261,13 +251,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -285,24 +317,36 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -321,18 +365,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -345,36 +377,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -393,24 +401,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -424,12 +420,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -452,6 +442,21 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -484,21 +489,6 @@
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -557,148 +547,148 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -712,52 +702,52 @@
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
+    <cellStyle name="输入" xfId="3" builtinId="20"/>
+    <cellStyle name="货币" xfId="4" builtinId="4"/>
+    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
+    <cellStyle name="差" xfId="7" builtinId="27"/>
+    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
+    <cellStyle name="超链接" xfId="10" builtinId="8"/>
+    <cellStyle name="百分比" xfId="11" builtinId="5"/>
+    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
+    <cellStyle name="注释" xfId="13" builtinId="10"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
     <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
+    <cellStyle name="标题" xfId="17" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
+    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
+    <cellStyle name="输出" xfId="24" builtinId="21"/>
+    <cellStyle name="计算" xfId="25" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
+    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
+    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
+    <cellStyle name="汇总" xfId="30" builtinId="25"/>
+    <cellStyle name="好" xfId="31" builtinId="26"/>
+    <cellStyle name="适中" xfId="32" builtinId="28"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
+    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
+    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
+    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
+    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
@@ -1029,15 +1019,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C29"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="26.375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="26.3796296296296" style="1" customWidth="1"/>
     <col min="3" max="3" width="10.25" style="1" customWidth="1"/>
     <col min="4" max="4" width="18.75" style="1" customWidth="1"/>
     <col min="5" max="5" width="20.75" style="1" customWidth="1"/>
-    <col min="6" max="6" width="20.8833333333333" style="1" customWidth="1"/>
-    <col min="7" max="7" width="20.6333333333333" style="1" customWidth="1"/>
+    <col min="6" max="6" width="20.8796296296296" style="1" customWidth="1"/>
+    <col min="7" max="7" width="20.6296296296296" style="1" customWidth="1"/>
     <col min="8" max="8" width="20" style="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
@@ -1317,6 +1307,9 @@
         <f t="shared" si="1"/>
         <v>10020</v>
       </c>
+      <c r="B22" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="C22" s="1">
         <f t="shared" si="0"/>
         <v>20020</v>

--- a/Assets/StreamingAssets/id注解.xlsx
+++ b/Assets/StreamingAssets/id注解.xlsx
@@ -1,20 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18468" windowHeight="10007"/>
+    <workbookView windowWidth="19755" windowHeight="11655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="22">
   <si>
     <t>id</t>
   </si>
@@ -77,12 +90,15 @@
   </si>
   <si>
     <t>测试用boss</t>
+  </si>
+  <si>
+    <t>虚拟摄像机</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -98,55 +114,19 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="等线"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -191,6 +171,21 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="等线"/>
       <charset val="0"/>
@@ -236,7 +231,28 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -251,49 +267,133 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -305,121 +405,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -442,21 +458,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -489,6 +490,21 @@
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -547,148 +563,148 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -702,52 +718,52 @@
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
-    <cellStyle name="输入" xfId="3" builtinId="20"/>
-    <cellStyle name="货币" xfId="4" builtinId="4"/>
-    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
-    <cellStyle name="差" xfId="7" builtinId="27"/>
-    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
-    <cellStyle name="超链接" xfId="10" builtinId="8"/>
-    <cellStyle name="百分比" xfId="11" builtinId="5"/>
-    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
-    <cellStyle name="注释" xfId="13" builtinId="10"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
     <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
-    <cellStyle name="标题" xfId="17" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
-    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="计算" xfId="25" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
-    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
-    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
-    <cellStyle name="汇总" xfId="30" builtinId="25"/>
-    <cellStyle name="好" xfId="31" builtinId="26"/>
-    <cellStyle name="适中" xfId="32" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
-    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
-    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
-    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
-    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
@@ -1019,15 +1035,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C29"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="26.3796296296296" style="1" customWidth="1"/>
+    <col min="2" max="2" width="26.3833333333333" style="1" customWidth="1"/>
     <col min="3" max="3" width="10.25" style="1" customWidth="1"/>
     <col min="4" max="4" width="18.75" style="1" customWidth="1"/>
     <col min="5" max="5" width="20.75" style="1" customWidth="1"/>
-    <col min="6" max="6" width="20.8796296296296" style="1" customWidth="1"/>
-    <col min="7" max="7" width="20.6296296296296" style="1" customWidth="1"/>
+    <col min="6" max="6" width="20.8833333333333" style="1" customWidth="1"/>
+    <col min="7" max="7" width="20.6333333333333" style="1" customWidth="1"/>
     <col min="8" max="8" width="20" style="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
@@ -1320,6 +1336,9 @@
         <f t="shared" si="1"/>
         <v>10021</v>
       </c>
+      <c r="B23" s="1" t="s">
+        <v>21</v>
+      </c>
       <c r="C23" s="1">
         <f t="shared" si="0"/>
         <v>20021</v>

--- a/Assets/StreamingAssets/id注解.xlsx
+++ b/Assets/StreamingAssets/id注解.xlsx
@@ -92,7 +92,7 @@
     <t>测试用boss</t>
   </si>
   <si>
-    <t>虚拟摄像机</t>
+    <t>恶龙boss</t>
   </si>
 </sst>
 </file>

--- a/Assets/StreamingAssets/id注解.xlsx
+++ b/Assets/StreamingAssets/id注解.xlsx
@@ -1,33 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19755" windowHeight="11655"/>
+    <workbookView windowWidth="18468" windowHeight="10007"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="24">
   <si>
     <t>id</t>
   </si>
@@ -93,12 +80,18 @@
   </si>
   <si>
     <t>恶龙boss</t>
+  </si>
+  <si>
+    <t>可穿墙主角</t>
+  </si>
+  <si>
+    <t>可穿墙箱子</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -114,6 +107,34 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -127,6 +148,14 @@
       <color rgb="FF800080"/>
       <name val="等线"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -171,14 +200,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF3F3F3F"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -186,7 +208,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFA7D00"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -194,6 +216,13 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="等线"/>
       <charset val="0"/>
@@ -202,57 +231,21 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -267,13 +260,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -291,24 +326,36 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -327,18 +374,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -351,36 +386,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -399,24 +410,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -430,12 +429,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -458,6 +451,21 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -490,21 +498,6 @@
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -563,148 +556,148 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -718,52 +711,52 @@
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
+    <cellStyle name="输入" xfId="3" builtinId="20"/>
+    <cellStyle name="货币" xfId="4" builtinId="4"/>
+    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
+    <cellStyle name="差" xfId="7" builtinId="27"/>
+    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
+    <cellStyle name="超链接" xfId="10" builtinId="8"/>
+    <cellStyle name="百分比" xfId="11" builtinId="5"/>
+    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
+    <cellStyle name="注释" xfId="13" builtinId="10"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
     <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
+    <cellStyle name="标题" xfId="17" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
+    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
+    <cellStyle name="输出" xfId="24" builtinId="21"/>
+    <cellStyle name="计算" xfId="25" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
+    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
+    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
+    <cellStyle name="汇总" xfId="30" builtinId="25"/>
+    <cellStyle name="好" xfId="31" builtinId="26"/>
+    <cellStyle name="适中" xfId="32" builtinId="28"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
+    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
+    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
+    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
+    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
@@ -1035,15 +1028,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C29"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="26.3833333333333" style="1" customWidth="1"/>
+    <col min="2" max="2" width="26.3796296296296" style="1" customWidth="1"/>
     <col min="3" max="3" width="10.25" style="1" customWidth="1"/>
     <col min="4" max="4" width="18.75" style="1" customWidth="1"/>
     <col min="5" max="5" width="20.75" style="1" customWidth="1"/>
-    <col min="6" max="6" width="20.8833333333333" style="1" customWidth="1"/>
-    <col min="7" max="7" width="20.6333333333333" style="1" customWidth="1"/>
+    <col min="6" max="6" width="20.8796296296296" style="1" customWidth="1"/>
+    <col min="7" max="7" width="20.6296296296296" style="1" customWidth="1"/>
     <col min="8" max="8" width="20" style="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
@@ -1349,6 +1342,9 @@
         <f t="shared" si="1"/>
         <v>10022</v>
       </c>
+      <c r="B24" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="C24" s="1">
         <f t="shared" si="0"/>
         <v>20022</v>
@@ -1358,6 +1354,9 @@
       <c r="A25" s="1">
         <f t="shared" si="1"/>
         <v>10023</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="C25" s="1">
         <f t="shared" si="0"/>

--- a/Assets/StreamingAssets/id注解.xlsx
+++ b/Assets/StreamingAssets/id注解.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="25">
   <si>
     <t>id</t>
   </si>
@@ -86,6 +86,9 @@
   </si>
   <si>
     <t>可穿墙箱子</t>
+  </si>
+  <si>
+    <t>可穿墙可锁定箱子</t>
   </si>
 </sst>
 </file>
@@ -1368,6 +1371,9 @@
         <f t="shared" si="1"/>
         <v>10024</v>
       </c>
+      <c r="B26" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="C26" s="1">
         <f t="shared" si="0"/>
         <v>20024</v>

--- a/Assets/StreamingAssets/id注解.xlsx
+++ b/Assets/StreamingAssets/id注解.xlsx
@@ -1,15 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18468" windowHeight="10007"/>
+    <workbookView windowWidth="19755" windowHeight="11655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -94,7 +107,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -110,55 +123,19 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="等线"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -203,6 +180,21 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="等线"/>
       <charset val="0"/>
@@ -248,7 +240,28 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -263,49 +276,133 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -317,121 +414,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -454,21 +467,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -501,6 +499,21 @@
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -559,148 +572,148 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -714,52 +727,52 @@
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
-    <cellStyle name="输入" xfId="3" builtinId="20"/>
-    <cellStyle name="货币" xfId="4" builtinId="4"/>
-    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
-    <cellStyle name="差" xfId="7" builtinId="27"/>
-    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
-    <cellStyle name="超链接" xfId="10" builtinId="8"/>
-    <cellStyle name="百分比" xfId="11" builtinId="5"/>
-    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
-    <cellStyle name="注释" xfId="13" builtinId="10"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
     <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
-    <cellStyle name="标题" xfId="17" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
-    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="计算" xfId="25" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
-    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
-    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
-    <cellStyle name="汇总" xfId="30" builtinId="25"/>
-    <cellStyle name="好" xfId="31" builtinId="26"/>
-    <cellStyle name="适中" xfId="32" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
-    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
-    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
-    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
-    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
@@ -1031,15 +1044,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C29"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="26.3796296296296" style="1" customWidth="1"/>
+    <col min="2" max="2" width="26.3833333333333" style="1" customWidth="1"/>
     <col min="3" max="3" width="10.25" style="1" customWidth="1"/>
     <col min="4" max="4" width="18.75" style="1" customWidth="1"/>
     <col min="5" max="5" width="20.75" style="1" customWidth="1"/>
-    <col min="6" max="6" width="20.8796296296296" style="1" customWidth="1"/>
-    <col min="7" max="7" width="20.6296296296296" style="1" customWidth="1"/>
+    <col min="6" max="6" width="20.8833333333333" style="1" customWidth="1"/>
+    <col min="7" max="7" width="20.6333333333333" style="1" customWidth="1"/>
     <col min="8" max="8" width="20" style="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="1"/>
   </cols>

--- a/Assets/StreamingAssets/id注解.xlsx
+++ b/Assets/StreamingAssets/id注解.xlsx
@@ -1,33 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19755" windowHeight="11655"/>
+    <workbookView windowWidth="18468" windowHeight="10007"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="26">
   <si>
     <t>id</t>
   </si>
@@ -102,12 +89,15 @@
   </si>
   <si>
     <t>可穿墙可锁定箱子</t>
+  </si>
+  <si>
+    <t>亮度墙（Tiles版）</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -123,6 +113,34 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -136,6 +154,14 @@
       <color rgb="FF800080"/>
       <name val="等线"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -180,14 +206,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF3F3F3F"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -195,7 +214,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFA7D00"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -203,6 +222,13 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="等线"/>
       <charset val="0"/>
@@ -211,57 +237,21 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -276,13 +266,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -300,24 +332,36 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -336,18 +380,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -360,36 +392,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -408,24 +416,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -439,12 +435,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -467,6 +457,21 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -499,21 +504,6 @@
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -572,148 +562,148 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -727,52 +717,52 @@
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
+    <cellStyle name="输入" xfId="3" builtinId="20"/>
+    <cellStyle name="货币" xfId="4" builtinId="4"/>
+    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
+    <cellStyle name="差" xfId="7" builtinId="27"/>
+    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
+    <cellStyle name="超链接" xfId="10" builtinId="8"/>
+    <cellStyle name="百分比" xfId="11" builtinId="5"/>
+    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
+    <cellStyle name="注释" xfId="13" builtinId="10"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
     <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
+    <cellStyle name="标题" xfId="17" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
+    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
+    <cellStyle name="输出" xfId="24" builtinId="21"/>
+    <cellStyle name="计算" xfId="25" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
+    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
+    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
+    <cellStyle name="汇总" xfId="30" builtinId="25"/>
+    <cellStyle name="好" xfId="31" builtinId="26"/>
+    <cellStyle name="适中" xfId="32" builtinId="28"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
+    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
+    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
+    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
+    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
@@ -1044,15 +1034,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C29"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="26.3833333333333" style="1" customWidth="1"/>
+    <col min="2" max="2" width="26.3796296296296" style="1" customWidth="1"/>
     <col min="3" max="3" width="10.25" style="1" customWidth="1"/>
     <col min="4" max="4" width="18.75" style="1" customWidth="1"/>
     <col min="5" max="5" width="20.75" style="1" customWidth="1"/>
-    <col min="6" max="6" width="20.8833333333333" style="1" customWidth="1"/>
-    <col min="7" max="7" width="20.6333333333333" style="1" customWidth="1"/>
+    <col min="6" max="6" width="20.8796296296296" style="1" customWidth="1"/>
+    <col min="7" max="7" width="20.6296296296296" style="1" customWidth="1"/>
     <col min="8" max="8" width="20" style="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
@@ -1397,6 +1387,9 @@
         <f t="shared" si="1"/>
         <v>10025</v>
       </c>
+      <c r="B27" s="1" t="s">
+        <v>25</v>
+      </c>
       <c r="C27" s="1">
         <f t="shared" si="0"/>
         <v>20025</v>

--- a/Assets/StreamingAssets/id注解.xlsx
+++ b/Assets/StreamingAssets/id注解.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="27">
   <si>
     <t>id</t>
   </si>
@@ -92,6 +92,9 @@
   </si>
   <si>
     <t>亮度墙（Tiles版）</t>
+  </si>
+  <si>
+    <t>不贴主角正常箱子</t>
   </si>
 </sst>
 </file>
@@ -1400,6 +1403,9 @@
         <f t="shared" si="1"/>
         <v>10026</v>
       </c>
+      <c r="B28" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="C28" s="1">
         <f t="shared" si="0"/>
         <v>20026</v>

--- a/Assets/StreamingAssets/id注解.xlsx
+++ b/Assets/StreamingAssets/id注解.xlsx
@@ -1,15 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18468" windowHeight="10007"/>
+    <workbookView windowWidth="19755" windowHeight="11655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -100,7 +113,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -116,55 +129,19 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="等线"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -209,6 +186,21 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="等线"/>
       <charset val="0"/>
@@ -254,7 +246,28 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -269,49 +282,133 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -323,121 +420,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -460,21 +473,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -507,6 +505,21 @@
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -565,148 +578,148 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -720,52 +733,52 @@
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
-    <cellStyle name="输入" xfId="3" builtinId="20"/>
-    <cellStyle name="货币" xfId="4" builtinId="4"/>
-    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
-    <cellStyle name="差" xfId="7" builtinId="27"/>
-    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
-    <cellStyle name="超链接" xfId="10" builtinId="8"/>
-    <cellStyle name="百分比" xfId="11" builtinId="5"/>
-    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
-    <cellStyle name="注释" xfId="13" builtinId="10"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
     <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
-    <cellStyle name="标题" xfId="17" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
-    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="计算" xfId="25" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
-    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
-    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
-    <cellStyle name="汇总" xfId="30" builtinId="25"/>
-    <cellStyle name="好" xfId="31" builtinId="26"/>
-    <cellStyle name="适中" xfId="32" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
-    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
-    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
-    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
-    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
@@ -1037,15 +1050,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C29"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="26.3796296296296" style="1" customWidth="1"/>
+    <col min="2" max="2" width="26.3833333333333" style="1" customWidth="1"/>
     <col min="3" max="3" width="10.25" style="1" customWidth="1"/>
     <col min="4" max="4" width="18.75" style="1" customWidth="1"/>
     <col min="5" max="5" width="20.75" style="1" customWidth="1"/>
-    <col min="6" max="6" width="20.8796296296296" style="1" customWidth="1"/>
-    <col min="7" max="7" width="20.6296296296296" style="1" customWidth="1"/>
+    <col min="6" max="6" width="20.8833333333333" style="1" customWidth="1"/>
+    <col min="7" max="7" width="20.6333333333333" style="1" customWidth="1"/>
     <col min="8" max="8" width="20" style="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="1"/>
   </cols>

--- a/Assets/StreamingAssets/id注解.xlsx
+++ b/Assets/StreamingAssets/id注解.xlsx
@@ -1,33 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19755" windowHeight="11655"/>
+    <workbookView windowWidth="18468" windowHeight="10007"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="28">
   <si>
     <t>id</t>
   </si>
@@ -108,12 +95,15 @@
   </si>
   <si>
     <t>不贴主角正常箱子</t>
+  </si>
+  <si>
+    <t>加强版史莱姆（不会被箱子和滑块打死）</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -129,6 +119,34 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -142,6 +160,14 @@
       <color rgb="FF800080"/>
       <name val="等线"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -186,14 +212,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF3F3F3F"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -201,7 +220,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFA7D00"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -209,6 +228,13 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="等线"/>
       <charset val="0"/>
@@ -217,57 +243,21 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -282,13 +272,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -306,24 +338,36 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -342,18 +386,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -366,36 +398,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -414,24 +422,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -445,12 +441,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -473,6 +463,21 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -505,21 +510,6 @@
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -578,148 +568,148 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -733,52 +723,52 @@
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
+    <cellStyle name="输入" xfId="3" builtinId="20"/>
+    <cellStyle name="货币" xfId="4" builtinId="4"/>
+    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
+    <cellStyle name="差" xfId="7" builtinId="27"/>
+    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
+    <cellStyle name="超链接" xfId="10" builtinId="8"/>
+    <cellStyle name="百分比" xfId="11" builtinId="5"/>
+    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
+    <cellStyle name="注释" xfId="13" builtinId="10"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
     <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
+    <cellStyle name="标题" xfId="17" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
+    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
+    <cellStyle name="输出" xfId="24" builtinId="21"/>
+    <cellStyle name="计算" xfId="25" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
+    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
+    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
+    <cellStyle name="汇总" xfId="30" builtinId="25"/>
+    <cellStyle name="好" xfId="31" builtinId="26"/>
+    <cellStyle name="适中" xfId="32" builtinId="28"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
+    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
+    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
+    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
+    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
@@ -1050,15 +1040,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C29"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="26.3833333333333" style="1" customWidth="1"/>
+    <col min="2" max="2" width="26.3796296296296" style="1" customWidth="1"/>
     <col min="3" max="3" width="10.25" style="1" customWidth="1"/>
     <col min="4" max="4" width="18.75" style="1" customWidth="1"/>
     <col min="5" max="5" width="20.75" style="1" customWidth="1"/>
-    <col min="6" max="6" width="20.8833333333333" style="1" customWidth="1"/>
-    <col min="7" max="7" width="20.6333333333333" style="1" customWidth="1"/>
+    <col min="6" max="6" width="20.8796296296296" style="1" customWidth="1"/>
+    <col min="7" max="7" width="20.6296296296296" style="1" customWidth="1"/>
     <col min="8" max="8" width="20" style="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
@@ -1429,6 +1419,9 @@
         <f t="shared" si="1"/>
         <v>10027</v>
       </c>
+      <c r="B29" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="C29" s="1">
         <f t="shared" si="0"/>
         <v>20027</v>

--- a/Assets/StreamingAssets/id注解.xlsx
+++ b/Assets/StreamingAssets/id注解.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="32">
   <si>
     <t>id</t>
   </si>
@@ -98,6 +98,18 @@
   </si>
   <si>
     <t>加强版史莱姆（不会被箱子和滑块打死）</t>
+  </si>
+  <si>
+    <t>随音量设置显示门</t>
+  </si>
+  <si>
+    <t>随相机设置显示门</t>
+  </si>
+  <si>
+    <t>随音量设置显示钥匙</t>
+  </si>
+  <si>
+    <t>随相机设置显示钥匙</t>
   </si>
 </sst>
 </file>
@@ -1039,7 +1051,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -1137,7 +1149,6 @@
         <v>6</v>
       </c>
       <c r="C7" s="1">
-        <f t="shared" si="0"/>
         <v>20005</v>
       </c>
     </row>
@@ -1425,6 +1436,38 @@
       <c r="C29" s="1">
         <f t="shared" si="0"/>
         <v>20027</v>
+      </c>
+    </row>
+    <row r="30" spans="2:3">
+      <c r="B30" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C30" s="1">
+        <v>20028</v>
+      </c>
+    </row>
+    <row r="31" spans="2:3">
+      <c r="B31" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C31" s="1">
+        <v>20029</v>
+      </c>
+    </row>
+    <row r="32" spans="2:3">
+      <c r="B32" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C32" s="1">
+        <v>20030</v>
+      </c>
+    </row>
+    <row r="33" spans="2:3">
+      <c r="B33" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C33" s="1">
+        <v>20031</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/StreamingAssets/id注解.xlsx
+++ b/Assets/StreamingAssets/id注解.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="29">
   <si>
     <t>id</t>
   </si>
@@ -100,16 +100,7 @@
     <t>加强版史莱姆（不会被箱子和滑块打死）</t>
   </si>
   <si>
-    <t>随音量设置显示门</t>
-  </si>
-  <si>
-    <t>随相机设置显示门</t>
-  </si>
-  <si>
-    <t>随音量设置显示钥匙</t>
-  </si>
-  <si>
-    <t>随相机设置显示钥匙</t>
+    <t>超级被墙挤死史莱姆</t>
   </si>
 </sst>
 </file>
@@ -1446,26 +1437,17 @@
         <v>20028</v>
       </c>
     </row>
-    <row r="31" spans="2:3">
-      <c r="B31" s="1" t="s">
-        <v>29</v>
-      </c>
+    <row r="31" spans="3:3">
       <c r="C31" s="1">
         <v>20029</v>
       </c>
     </row>
-    <row r="32" spans="2:3">
-      <c r="B32" s="1" t="s">
-        <v>30</v>
-      </c>
+    <row r="32" spans="3:3">
       <c r="C32" s="1">
         <v>20030</v>
       </c>
     </row>
-    <row r="33" spans="2:3">
-      <c r="B33" s="1" t="s">
-        <v>31</v>
-      </c>
+    <row r="33" spans="3:3">
       <c r="C33" s="1">
         <v>20031</v>
       </c>

--- a/Assets/StreamingAssets/id注解.xlsx
+++ b/Assets/StreamingAssets/id注解.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="30">
   <si>
     <t>id</t>
   </si>
@@ -101,6 +101,9 @@
   </si>
   <si>
     <t>超级被墙挤死史莱姆</t>
+  </si>
+  <si>
+    <t>只可拖动角色</t>
   </si>
 </sst>
 </file>
@@ -1437,7 +1440,10 @@
         <v>20028</v>
       </c>
     </row>
-    <row r="31" spans="3:3">
+    <row r="31" spans="2:3">
+      <c r="B31" s="1" t="s">
+        <v>29</v>
+      </c>
       <c r="C31" s="1">
         <v>20029</v>
       </c>

--- a/Assets/StreamingAssets/id注解.xlsx
+++ b/Assets/StreamingAssets/id注解.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="31">
   <si>
     <t>id</t>
   </si>
@@ -100,10 +100,13 @@
     <t>加强版史莱姆（不会被箱子和滑块打死）</t>
   </si>
   <si>
-    <t>超级被墙挤死史莱姆</t>
+    <t>可拖动超级被墙挤死史莱姆</t>
   </si>
   <si>
     <t>只可拖动角色</t>
+  </si>
+  <si>
+    <t>可拖动箱子</t>
   </si>
 </sst>
 </file>
@@ -1448,7 +1451,10 @@
         <v>20029</v>
       </c>
     </row>
-    <row r="32" spans="3:3">
+    <row r="32" spans="2:3">
+      <c r="B32" s="1" t="s">
+        <v>30</v>
+      </c>
       <c r="C32" s="1">
         <v>20030</v>
       </c>

--- a/Assets/StreamingAssets/id注解.xlsx
+++ b/Assets/StreamingAssets/id注解.xlsx
@@ -1,15 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18468" windowHeight="10007"/>
+    <workbookView windowWidth="19755" windowHeight="11655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -112,7 +125,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -128,55 +141,19 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="等线"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -221,6 +198,21 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="等线"/>
       <charset val="0"/>
@@ -266,7 +258,28 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -281,49 +294,133 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -335,121 +432,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -472,21 +485,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -519,6 +517,21 @@
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -577,148 +590,148 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -732,52 +745,52 @@
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
-    <cellStyle name="输入" xfId="3" builtinId="20"/>
-    <cellStyle name="货币" xfId="4" builtinId="4"/>
-    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
-    <cellStyle name="差" xfId="7" builtinId="27"/>
-    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
-    <cellStyle name="超链接" xfId="10" builtinId="8"/>
-    <cellStyle name="百分比" xfId="11" builtinId="5"/>
-    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
-    <cellStyle name="注释" xfId="13" builtinId="10"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
     <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
-    <cellStyle name="标题" xfId="17" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
-    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="计算" xfId="25" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
-    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
-    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
-    <cellStyle name="汇总" xfId="30" builtinId="25"/>
-    <cellStyle name="好" xfId="31" builtinId="26"/>
-    <cellStyle name="适中" xfId="32" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
-    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
-    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
-    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
-    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
@@ -1048,16 +1061,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C33"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="2"/>
+  <dimension ref="A1:C35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="26.3796296296296" style="1" customWidth="1"/>
+    <col min="2" max="2" width="26.3833333333333" style="1" customWidth="1"/>
     <col min="3" max="3" width="10.25" style="1" customWidth="1"/>
     <col min="4" max="4" width="18.75" style="1" customWidth="1"/>
     <col min="5" max="5" width="20.75" style="1" customWidth="1"/>
-    <col min="6" max="6" width="20.8796296296296" style="1" customWidth="1"/>
-    <col min="7" max="7" width="20.6296296296296" style="1" customWidth="1"/>
+    <col min="6" max="6" width="20.8833333333333" style="1" customWidth="1"/>
+    <col min="7" max="7" width="20.6333333333333" style="1" customWidth="1"/>
     <col min="8" max="8" width="20" style="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
@@ -1094,7 +1107,7 @@
         <v>4</v>
       </c>
       <c r="C3" s="1">
-        <f t="shared" ref="C3:C29" si="0">SUM(A3)+10000</f>
+        <f t="shared" ref="C3:C35" si="0">SUM(A3)+10000</f>
         <v>20001</v>
       </c>
     </row>
@@ -1126,7 +1139,7 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="1">
-        <f t="shared" ref="A6:A29" si="1">SUM(A5)+1</f>
+        <f t="shared" ref="A6:A35" si="1">SUM(A5)+1</f>
         <v>10004</v>
       </c>
       <c r="B6" s="1" t="s">
@@ -1435,33 +1448,73 @@
         <v>20027</v>
       </c>
     </row>
-    <row r="30" spans="2:3">
+    <row r="30" spans="1:3">
+      <c r="A30" s="1">
+        <f t="shared" si="1"/>
+        <v>10028</v>
+      </c>
       <c r="B30" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C30" s="1">
+        <f t="shared" si="0"/>
         <v>20028</v>
       </c>
     </row>
-    <row r="31" spans="2:3">
+    <row r="31" spans="1:3">
+      <c r="A31" s="1">
+        <f t="shared" si="1"/>
+        <v>10029</v>
+      </c>
       <c r="B31" s="1" t="s">
         <v>29</v>
       </c>
       <c r="C31" s="1">
+        <f t="shared" si="0"/>
         <v>20029</v>
       </c>
     </row>
-    <row r="32" spans="2:3">
+    <row r="32" spans="1:3">
+      <c r="A32" s="1">
+        <f t="shared" si="1"/>
+        <v>10030</v>
+      </c>
       <c r="B32" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C32" s="1">
+        <f t="shared" si="0"/>
         <v>20030</v>
       </c>
     </row>
-    <row r="33" spans="3:3">
+    <row r="33" spans="1:3">
+      <c r="A33" s="1">
+        <f t="shared" si="1"/>
+        <v>10031</v>
+      </c>
       <c r="C33" s="1">
+        <f t="shared" si="0"/>
         <v>20031</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="1">
+        <f t="shared" si="1"/>
+        <v>10032</v>
+      </c>
+      <c r="C34" s="1">
+        <f t="shared" si="0"/>
+        <v>20032</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" s="1">
+        <f t="shared" si="1"/>
+        <v>10033</v>
+      </c>
+      <c r="C35" s="1">
+        <f t="shared" si="0"/>
+        <v>20033</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/StreamingAssets/id注解.xlsx
+++ b/Assets/StreamingAssets/id注解.xlsx
@@ -1,33 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19755" windowHeight="11655"/>
+    <workbookView windowWidth="18468" windowHeight="10007"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="32">
   <si>
     <t>id</t>
   </si>
@@ -120,12 +107,15 @@
   </si>
   <si>
     <t>可拖动箱子</t>
+  </si>
+  <si>
+    <t>亮度墙（Tiles版无碰撞）</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -141,6 +131,34 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -154,6 +172,14 @@
       <color rgb="FF800080"/>
       <name val="等线"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -198,14 +224,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF3F3F3F"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -213,7 +232,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFA7D00"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -221,6 +240,13 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="等线"/>
       <charset val="0"/>
@@ -229,57 +255,21 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -294,13 +284,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -318,24 +350,36 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -354,18 +398,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -378,36 +410,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -426,24 +434,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -457,12 +453,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -485,6 +475,21 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -517,21 +522,6 @@
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -590,148 +580,148 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -745,52 +735,52 @@
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
+    <cellStyle name="输入" xfId="3" builtinId="20"/>
+    <cellStyle name="货币" xfId="4" builtinId="4"/>
+    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
+    <cellStyle name="差" xfId="7" builtinId="27"/>
+    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
+    <cellStyle name="超链接" xfId="10" builtinId="8"/>
+    <cellStyle name="百分比" xfId="11" builtinId="5"/>
+    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
+    <cellStyle name="注释" xfId="13" builtinId="10"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
     <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
+    <cellStyle name="标题" xfId="17" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
+    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
+    <cellStyle name="输出" xfId="24" builtinId="21"/>
+    <cellStyle name="计算" xfId="25" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
+    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
+    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
+    <cellStyle name="汇总" xfId="30" builtinId="25"/>
+    <cellStyle name="好" xfId="31" builtinId="26"/>
+    <cellStyle name="适中" xfId="32" builtinId="28"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
+    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
+    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
+    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
+    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
@@ -1062,15 +1052,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C35"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="26.3833333333333" style="1" customWidth="1"/>
+    <col min="2" max="2" width="26.3796296296296" style="1" customWidth="1"/>
     <col min="3" max="3" width="10.25" style="1" customWidth="1"/>
     <col min="4" max="4" width="18.75" style="1" customWidth="1"/>
     <col min="5" max="5" width="20.75" style="1" customWidth="1"/>
-    <col min="6" max="6" width="20.8833333333333" style="1" customWidth="1"/>
-    <col min="7" max="7" width="20.6333333333333" style="1" customWidth="1"/>
+    <col min="6" max="6" width="20.8796296296296" style="1" customWidth="1"/>
+    <col min="7" max="7" width="20.6296296296296" style="1" customWidth="1"/>
     <col min="8" max="8" width="20" style="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
@@ -1492,6 +1482,9 @@
         <f t="shared" si="1"/>
         <v>10031</v>
       </c>
+      <c r="B33" s="1" t="s">
+        <v>31</v>
+      </c>
       <c r="C33" s="1">
         <f t="shared" si="0"/>
         <v>20031</v>

--- a/Assets/StreamingAssets/id注解.xlsx
+++ b/Assets/StreamingAssets/id注解.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="33">
   <si>
     <t>id</t>
   </si>
@@ -36,6 +36,12 @@
   </si>
   <si>
     <t>·效果id</t>
+  </si>
+  <si>
+    <t>气泡事件id</t>
+  </si>
+  <si>
+    <t>对应名称</t>
   </si>
   <si>
     <t>主角</t>
@@ -1061,8 +1067,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C35"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="2"/>
+  <dimension ref="A1:E35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
     <col min="2" max="2" width="26.3833333333333" style="1" customWidth="1"/>
@@ -1075,7 +1081,7 @@
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1085,43 +1091,60 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="1">
         <v>10000</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C2" s="1">
         <f>SUM(A2)+10000</f>
         <v>20000</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
+      <c r="D2" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="1">
         <f>SUM(A2)+1</f>
         <v>10001</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C3" s="1">
         <f t="shared" ref="C3:C35" si="0">SUM(A3)+10000</f>
         <v>20001</v>
       </c>
-    </row>
-    <row r="4" spans="1:3">
+      <c r="D3" s="1">
+        <f>SUM(D2+1)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" s="1">
         <f>SUM(A3)+1</f>
         <v>10002</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C4" s="1">
         <f t="shared" si="0"/>
         <v>20002</v>
+      </c>
+      <c r="D4" s="1">
+        <f>SUM(D3+1)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1130,7 +1153,7 @@
         <v>10003</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C5" s="1">
         <f t="shared" si="0"/>
@@ -1143,7 +1166,7 @@
         <v>10004</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C6" s="1">
         <f t="shared" si="0"/>
@@ -1156,7 +1179,7 @@
         <v>10005</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C7" s="1">
         <v>20005</v>
@@ -1168,7 +1191,7 @@
         <v>10006</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C8" s="1">
         <f t="shared" si="0"/>
@@ -1181,7 +1204,7 @@
         <v>10007</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C9" s="1">
         <f t="shared" si="0"/>
@@ -1194,7 +1217,7 @@
         <v>10008</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C10" s="1">
         <f t="shared" si="0"/>
@@ -1207,7 +1230,7 @@
         <v>10009</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C11" s="1">
         <f t="shared" si="0"/>
@@ -1220,7 +1243,7 @@
         <v>10010</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C12" s="1">
         <f t="shared" si="0"/>
@@ -1233,7 +1256,7 @@
         <v>10011</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C13" s="1">
         <f t="shared" si="0"/>
@@ -1246,7 +1269,7 @@
         <v>10012</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C14" s="1">
         <f t="shared" si="0"/>
@@ -1259,7 +1282,7 @@
         <v>10013</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C15" s="1">
         <f t="shared" si="0"/>
@@ -1272,7 +1295,7 @@
         <v>10014</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C16" s="1">
         <f t="shared" si="0"/>
@@ -1285,7 +1308,7 @@
         <v>10015</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C17" s="1">
         <f t="shared" si="0"/>
@@ -1298,7 +1321,7 @@
         <v>10016</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C18" s="1">
         <f t="shared" si="0"/>
@@ -1311,7 +1334,7 @@
         <v>10017</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C19" s="1">
         <f t="shared" si="0"/>
@@ -1324,7 +1347,7 @@
         <v>10018</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C20" s="1">
         <f t="shared" si="0"/>
@@ -1337,7 +1360,7 @@
         <v>10019</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C21" s="1">
         <f t="shared" si="0"/>
@@ -1350,7 +1373,7 @@
         <v>10020</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C22" s="1">
         <f t="shared" si="0"/>
@@ -1363,7 +1386,7 @@
         <v>10021</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C23" s="1">
         <f t="shared" si="0"/>
@@ -1376,7 +1399,7 @@
         <v>10022</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C24" s="1">
         <f t="shared" si="0"/>
@@ -1389,7 +1412,7 @@
         <v>10023</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C25" s="1">
         <f t="shared" si="0"/>
@@ -1402,7 +1425,7 @@
         <v>10024</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C26" s="1">
         <f t="shared" si="0"/>
@@ -1415,7 +1438,7 @@
         <v>10025</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C27" s="1">
         <f t="shared" si="0"/>
@@ -1428,7 +1451,7 @@
         <v>10026</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C28" s="1">
         <f t="shared" si="0"/>
@@ -1441,7 +1464,7 @@
         <v>10027</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C29" s="1">
         <f t="shared" si="0"/>
@@ -1454,7 +1477,7 @@
         <v>10028</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C30" s="1">
         <f t="shared" si="0"/>
@@ -1467,7 +1490,7 @@
         <v>10029</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C31" s="1">
         <f t="shared" si="0"/>
@@ -1480,7 +1503,7 @@
         <v>10030</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C32" s="1">
         <f t="shared" si="0"/>

--- a/Assets/StreamingAssets/id注解.xlsx
+++ b/Assets/StreamingAssets/id注解.xlsx
@@ -1,33 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19755" windowHeight="11655"/>
+    <workbookView windowWidth="18468" windowHeight="10007"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="35">
   <si>
     <t>id</t>
   </si>
@@ -126,12 +113,18 @@
   </si>
   <si>
     <t>可拖动箱子</t>
+  </si>
+  <si>
+    <t>只显示亮度墙</t>
+  </si>
+  <si>
+    <t>公主</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -147,6 +140,34 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -160,6 +181,14 @@
       <color rgb="FF800080"/>
       <name val="等线"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -204,14 +233,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF3F3F3F"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -219,7 +241,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFA7D00"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -227,6 +249,13 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="等线"/>
       <charset val="0"/>
@@ -235,57 +264,21 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -300,13 +293,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -324,24 +359,36 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -360,18 +407,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -384,36 +419,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -432,24 +443,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -463,12 +462,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -491,6 +484,21 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -523,21 +531,6 @@
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -596,148 +589,148 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -751,52 +744,52 @@
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
+    <cellStyle name="输入" xfId="3" builtinId="20"/>
+    <cellStyle name="货币" xfId="4" builtinId="4"/>
+    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
+    <cellStyle name="差" xfId="7" builtinId="27"/>
+    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
+    <cellStyle name="超链接" xfId="10" builtinId="8"/>
+    <cellStyle name="百分比" xfId="11" builtinId="5"/>
+    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
+    <cellStyle name="注释" xfId="13" builtinId="10"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
     <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
+    <cellStyle name="标题" xfId="17" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
+    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
+    <cellStyle name="输出" xfId="24" builtinId="21"/>
+    <cellStyle name="计算" xfId="25" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
+    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
+    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
+    <cellStyle name="汇总" xfId="30" builtinId="25"/>
+    <cellStyle name="好" xfId="31" builtinId="26"/>
+    <cellStyle name="适中" xfId="32" builtinId="28"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
+    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
+    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
+    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
+    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
@@ -1068,15 +1061,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E35"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="26.3833333333333" style="1" customWidth="1"/>
+    <col min="2" max="2" width="26.3796296296296" style="1" customWidth="1"/>
     <col min="3" max="3" width="10.25" style="1" customWidth="1"/>
     <col min="4" max="4" width="18.75" style="1" customWidth="1"/>
     <col min="5" max="5" width="20.75" style="1" customWidth="1"/>
-    <col min="6" max="6" width="20.8833333333333" style="1" customWidth="1"/>
-    <col min="7" max="7" width="20.6333333333333" style="1" customWidth="1"/>
+    <col min="6" max="6" width="20.8796296296296" style="1" customWidth="1"/>
+    <col min="7" max="7" width="20.6296296296296" style="1" customWidth="1"/>
     <col min="8" max="8" width="20" style="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
@@ -1515,6 +1508,9 @@
         <f t="shared" si="1"/>
         <v>10031</v>
       </c>
+      <c r="B33" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="C33" s="1">
         <f t="shared" si="0"/>
         <v>20031</v>
@@ -1524,6 +1520,9 @@
       <c r="A34" s="1">
         <f t="shared" si="1"/>
         <v>10032</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="C34" s="1">
         <f t="shared" si="0"/>

--- a/Assets/StreamingAssets/id注解.xlsx
+++ b/Assets/StreamingAssets/id注解.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="37">
   <si>
     <t>id</t>
   </si>
@@ -119,6 +119,12 @@
   </si>
   <si>
     <t>公主</t>
+  </si>
+  <si>
+    <t>笼子</t>
+  </si>
+  <si>
+    <t>火焰</t>
   </si>
 </sst>
 </file>
@@ -1060,7 +1066,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -1534,9 +1540,20 @@
         <f t="shared" si="1"/>
         <v>10033</v>
       </c>
+      <c r="B35" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="C35" s="1">
         <f t="shared" si="0"/>
         <v>20033</v>
+      </c>
+    </row>
+    <row r="36" spans="2:3">
+      <c r="B36" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C36" s="1">
+        <v>20034</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/StreamingAssets/id注解.xlsx
+++ b/Assets/StreamingAssets/id注解.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="39">
   <si>
     <t>id</t>
   </si>
@@ -125,6 +125,12 @@
   </si>
   <si>
     <t>火焰</t>
+  </si>
+  <si>
+    <t>脆弱的龙</t>
+  </si>
+  <si>
+    <t>虚拟相机滑块</t>
   </si>
 </sst>
 </file>
@@ -1066,7 +1072,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -1556,6 +1562,22 @@
         <v>20034</v>
       </c>
     </row>
+    <row r="37" spans="2:3">
+      <c r="B37" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C37" s="1">
+        <v>20035</v>
+      </c>
+    </row>
+    <row r="38" spans="2:3">
+      <c r="B38" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C38" s="1">
+        <v>20036</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/Assets/StreamingAssets/id注解.xlsx
+++ b/Assets/StreamingAssets/id注解.xlsx
@@ -1,15 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18468" windowHeight="10007"/>
+    <workbookView windowWidth="19755" windowHeight="11655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -136,7 +149,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -152,34 +165,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -196,6 +181,45 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="3"/>
@@ -205,41 +229,9 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF3F3F76"/>
       <name val="等线"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -290,7 +282,28 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -305,49 +318,133 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -359,121 +456,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -496,21 +509,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -543,6 +541,21 @@
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -601,148 +614,148 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -756,52 +769,52 @@
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
-    <cellStyle name="输入" xfId="3" builtinId="20"/>
-    <cellStyle name="货币" xfId="4" builtinId="4"/>
-    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
-    <cellStyle name="差" xfId="7" builtinId="27"/>
-    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
-    <cellStyle name="超链接" xfId="10" builtinId="8"/>
-    <cellStyle name="百分比" xfId="11" builtinId="5"/>
-    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
-    <cellStyle name="注释" xfId="13" builtinId="10"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
     <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
-    <cellStyle name="标题" xfId="17" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
-    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="计算" xfId="25" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
-    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
-    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
-    <cellStyle name="汇总" xfId="30" builtinId="25"/>
-    <cellStyle name="好" xfId="31" builtinId="26"/>
-    <cellStyle name="适中" xfId="32" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
-    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
-    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
-    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
-    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
@@ -1072,16 +1085,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E38"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="4"/>
+  <dimension ref="A1:E42"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="26.3796296296296" style="1" customWidth="1"/>
+    <col min="2" max="2" width="26.3833333333333" style="1" customWidth="1"/>
     <col min="3" max="3" width="10.25" style="1" customWidth="1"/>
     <col min="4" max="4" width="18.75" style="1" customWidth="1"/>
     <col min="5" max="5" width="20.75" style="1" customWidth="1"/>
-    <col min="6" max="6" width="20.8796296296296" style="1" customWidth="1"/>
-    <col min="7" max="7" width="20.6296296296296" style="1" customWidth="1"/>
+    <col min="6" max="6" width="20.8833333333333" style="1" customWidth="1"/>
+    <col min="7" max="7" width="20.6333333333333" style="1" customWidth="1"/>
     <col min="8" max="8" width="20" style="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
@@ -1127,7 +1140,7 @@
         <v>6</v>
       </c>
       <c r="C3" s="1">
-        <f t="shared" ref="C3:C35" si="0">SUM(A3)+10000</f>
+        <f t="shared" ref="C3:C42" si="0">SUM(A3)+10000</f>
         <v>20001</v>
       </c>
       <c r="D3" s="1">
@@ -1167,7 +1180,7 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="1">
-        <f t="shared" ref="A6:A35" si="1">SUM(A5)+1</f>
+        <f t="shared" ref="A6:A41" si="1">SUM(A5)+1</f>
         <v>10004</v>
       </c>
       <c r="B6" s="1" t="s">
@@ -1554,28 +1567,83 @@
         <v>20033</v>
       </c>
     </row>
-    <row r="36" spans="2:3">
+    <row r="36" spans="1:3">
+      <c r="A36" s="1">
+        <f t="shared" si="1"/>
+        <v>10034</v>
+      </c>
       <c r="B36" s="1" t="s">
         <v>36</v>
       </c>
       <c r="C36" s="1">
+        <f t="shared" si="0"/>
         <v>20034</v>
       </c>
     </row>
-    <row r="37" spans="2:3">
+    <row r="37" spans="1:3">
+      <c r="A37" s="1">
+        <f t="shared" si="1"/>
+        <v>10035</v>
+      </c>
       <c r="B37" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C37" s="1">
+        <f t="shared" si="0"/>
         <v>20035</v>
       </c>
     </row>
-    <row r="38" spans="2:3">
+    <row r="38" spans="1:3">
+      <c r="A38" s="1">
+        <f t="shared" si="1"/>
+        <v>10036</v>
+      </c>
       <c r="B38" s="1" t="s">
         <v>38</v>
       </c>
       <c r="C38" s="1">
+        <f t="shared" si="0"/>
         <v>20036</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" s="1">
+        <f t="shared" si="1"/>
+        <v>10037</v>
+      </c>
+      <c r="C39" s="1">
+        <f t="shared" si="0"/>
+        <v>20037</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" s="1">
+        <f t="shared" si="1"/>
+        <v>10038</v>
+      </c>
+      <c r="C40" s="1">
+        <f t="shared" si="0"/>
+        <v>20038</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" s="1">
+        <f t="shared" si="1"/>
+        <v>10039</v>
+      </c>
+      <c r="C41" s="1">
+        <f t="shared" si="0"/>
+        <v>20039</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" s="1">
+        <f>SUM(A41)+1</f>
+        <v>10040</v>
+      </c>
+      <c r="C42" s="1">
+        <f t="shared" si="0"/>
+        <v>20040</v>
       </c>
     </row>
   </sheetData>
